--- a/public/informes-templates/INFORME DE UPS .xlsx
+++ b/public/informes-templates/INFORME DE UPS .xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6092C8D5-E142-4B5A-B84F-0A9B9D18AB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2B23CF6-31EE-4243-88AA-3D593949A1B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,39 +15,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="83">
-  <si>
-    <t>INFORME DE SERVICIO</t>
-  </si>
-  <si>
-    <t>EMPRESA / CLIENTE</t>
-  </si>
-  <si>
-    <t>CONTACTO</t>
-  </si>
-  <si>
-    <t>ORDEN DE COMPRA</t>
-  </si>
-  <si>
-    <t>COT</t>
-  </si>
-  <si>
-    <t>LINEA / AREA</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="74">
   <si>
     <t xml:space="preserve">DESCRIPCION </t>
   </si>
   <si>
-    <t>TIPO</t>
-  </si>
-  <si>
     <t>CANTIDAD</t>
-  </si>
-  <si>
-    <t>FECHA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EQUIPO 1 </t>
   </si>
   <si>
     <t>DATOS DEL EQUIPO</t>
@@ -270,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -310,25 +283,6 @@
       <i/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="20"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -381,8 +335,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -407,8 +367,14 @@
         <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="16">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -585,11 +551,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -606,10 +587,7 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -618,10 +596,10 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -629,126 +607,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -768,17 +626,191 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -795,55 +827,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1047,24 +1030,24 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:Y363"/>
+  <dimension ref="A1:Y364"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="8" width="18.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15"/>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="16"/>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="24"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
@@ -1083,15 +1066,15 @@
       <c r="Y1" s="1"/>
     </row>
     <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18"/>
-      <c r="G2" s="18"/>
-      <c r="H2" s="18"/>
-      <c r="I2" s="19"/>
+      <c r="A2" s="43"/>
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="44"/>
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
@@ -1110,17 +1093,15 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="16"/>
+      <c r="A3" s="78"/>
+      <c r="B3" s="79"/>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
+      <c r="I3" s="80"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
@@ -1139,17 +1120,15 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="21"/>
-      <c r="B4" s="22"/>
-      <c r="C4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="16"/>
+      <c r="A4" s="47"/>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
@@ -1168,17 +1147,17 @@
       <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="21"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="3" t="s">
-        <v>3</v>
+      <c r="A5" s="42" t="s">
+        <v>2</v>
       </c>
-      <c r="D5" s="23"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="16"/>
+      <c r="B5" s="55"/>
+      <c r="C5" s="55"/>
+      <c r="D5" s="55"/>
+      <c r="E5" s="55"/>
+      <c r="F5" s="55"/>
+      <c r="G5" s="55"/>
+      <c r="H5" s="55"/>
+      <c r="I5" s="56"/>
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
@@ -1197,17 +1176,27 @@
       <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="21"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="3" t="s">
+      <c r="A6" s="52" t="s">
+        <v>3</v>
+      </c>
+      <c r="B6" s="53"/>
+      <c r="C6" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="23"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="16"/>
+      <c r="D6" s="54"/>
+      <c r="E6" s="49" t="s">
+        <v>5</v>
+      </c>
+      <c r="F6" s="21"/>
+      <c r="G6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
@@ -1226,17 +1215,15 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="21"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="15"/>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
-      <c r="I7" s="16"/>
+      <c r="A7" s="63"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="65"/>
+      <c r="D7" s="66"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1255,17 +1242,19 @@
       <c r="Y7" s="1"/>
     </row>
     <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="21"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="3" t="s">
-        <v>6</v>
+      <c r="A8" s="3" t="s">
+        <v>9</v>
       </c>
-      <c r="D8" s="24"/>
-      <c r="E8" s="15"/>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
-      <c r="H8" s="15"/>
-      <c r="I8" s="16"/>
+      <c r="B8" s="50" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="57"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="59"/>
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
@@ -1284,17 +1273,15 @@
       <c r="Y8" s="1"/>
     </row>
     <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="16"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="60"/>
+      <c r="D9" s="61"/>
+      <c r="E9" s="61"/>
+      <c r="F9" s="61"/>
+      <c r="G9" s="61"/>
+      <c r="H9" s="61"/>
+      <c r="I9" s="62"/>
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
@@ -1313,17 +1300,19 @@
       <c r="Y9" s="1"/>
     </row>
     <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="3" t="s">
-        <v>8</v>
+      <c r="A10" s="25" t="s">
+        <v>11</v>
       </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="16"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
@@ -1342,17 +1331,19 @@
       <c r="Y10" s="1"/>
     </row>
     <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="3" t="s">
-        <v>9</v>
+      <c r="A11" s="2" t="s">
+        <v>13</v>
       </c>
-      <c r="D11" s="23"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="16"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="38"/>
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G11" s="6"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14"/>
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
@@ -1371,15 +1362,19 @@
       <c r="Y11" s="1"/>
     </row>
     <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="25"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="A12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16"/>
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
@@ -1398,19 +1393,19 @@
       <c r="Y12" s="1"/>
     </row>
     <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="26" t="s">
-        <v>10</v>
+      <c r="A13" s="2" t="s">
+        <v>15</v>
       </c>
-      <c r="B13" s="16"/>
-      <c r="C13" s="27" t="s">
-        <v>11</v>
+      <c r="B13" s="6"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="2" t="s">
+        <v>15</v>
       </c>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="29"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
@@ -1429,27 +1424,19 @@
       <c r="Y13" s="1"/>
     </row>
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="21"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E14" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" s="29"/>
-      <c r="G14" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>17</v>
+      <c r="B14" s="4"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="2" t="s">
+        <v>16</v>
       </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="16"/>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
@@ -1468,15 +1455,19 @@
       <c r="Y14" s="1"/>
     </row>
     <row r="15" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="21"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
+      <c r="A15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="6"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="6"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="16"/>
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
@@ -1495,17 +1486,17 @@
       <c r="Y15" s="1"/>
     </row>
     <row r="16" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="21"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="32" t="s">
-        <v>19</v>
+      <c r="B16" s="4"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="2" t="s">
+        <v>18</v>
       </c>
-      <c r="E16" s="31"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
+      <c r="G16" s="4"/>
       <c r="H16" s="15"/>
       <c r="I16" s="16"/>
       <c r="J16" s="1"/>
@@ -1526,15 +1517,19 @@
       <c r="Y16" s="1"/>
     </row>
     <row r="17" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="17"/>
-      <c r="B17" s="19"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="19"/>
+      <c r="A17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="4"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="16"/>
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
@@ -1553,19 +1548,19 @@
       <c r="Y17" s="1"/>
     </row>
     <row r="18" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="34" t="s">
+      <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="15"/>
+      <c r="B18" s="4"/>
       <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="34" t="s">
-        <v>21</v>
+      <c r="D18" s="16"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="2" t="s">
+        <v>20</v>
       </c>
-      <c r="G18" s="15"/>
+      <c r="G18" s="4"/>
       <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
+      <c r="I18" s="16"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
@@ -1585,18 +1580,18 @@
     </row>
     <row r="19" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="4"/>
-      <c r="C19" s="54"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="35"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="39"/>
       <c r="F19" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="54"/>
-      <c r="I19" s="55"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="16"/>
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
@@ -1616,18 +1611,18 @@
     </row>
     <row r="20" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="4"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="57"/>
-      <c r="E20" s="36"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="39"/>
       <c r="F20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
-      <c r="G20" s="7"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="57"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="16"/>
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
@@ -1647,18 +1642,18 @@
     </row>
     <row r="21" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
-      <c r="B21" s="7"/>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="36"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="39"/>
       <c r="F21" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
-      <c r="G21" s="7"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="16"/>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
@@ -1678,18 +1673,18 @@
     </row>
     <row r="22" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B22" s="4"/>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="36"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="39"/>
       <c r="F22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G22" s="4"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="57"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="16"/>
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
@@ -1709,18 +1704,18 @@
     </row>
     <row r="23" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
-      <c r="B23" s="7"/>
-      <c r="C23" s="56"/>
-      <c r="D23" s="57"/>
-      <c r="E23" s="36"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="39"/>
       <c r="F23" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="57"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="18"/>
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
@@ -1739,19 +1734,23 @@
       <c r="Y23" s="1"/>
     </row>
     <row r="24" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="41" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="21"/>
+      <c r="C24" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="56"/>
-      <c r="D24" s="57"/>
-      <c r="E24" s="36"/>
-      <c r="F24" s="2" t="s">
-        <v>27</v>
+      <c r="D24" s="24"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="41" t="s">
+        <v>26</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="56"/>
-      <c r="I24" s="57"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="42" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="24"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
@@ -1770,19 +1769,17 @@
       <c r="Y24" s="1"/>
     </row>
     <row r="25" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>28</v>
+      <c r="A25" s="45"/>
+      <c r="B25" s="44"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="44"/>
+      <c r="E25" s="40"/>
+      <c r="F25" s="46" t="s">
+        <v>29</v>
       </c>
-      <c r="B25" s="4"/>
-      <c r="C25" s="56"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="36"/>
-      <c r="F25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="56"/>
-      <c r="I25" s="57"/>
+      <c r="G25" s="44"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="44"/>
       <c r="J25" s="1"/>
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
@@ -1801,19 +1798,17 @@
       <c r="Y25" s="1"/>
     </row>
     <row r="26" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
-        <v>29</v>
+      <c r="A26" s="37" t="s">
+        <v>30</v>
       </c>
-      <c r="B26" s="4"/>
-      <c r="C26" s="56"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="36"/>
-      <c r="F26" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="56"/>
-      <c r="I26" s="57"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="20"/>
+      <c r="I26" s="21"/>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
@@ -1832,19 +1827,15 @@
       <c r="Y26" s="1"/>
     </row>
     <row r="27" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="56"/>
-      <c r="D27" s="57"/>
-      <c r="E27" s="36"/>
-      <c r="F27" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G27" s="4"/>
-      <c r="H27" s="56"/>
-      <c r="I27" s="57"/>
+      <c r="A27" s="67"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="67"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="69"/>
+      <c r="G27" s="67"/>
+      <c r="H27" s="68"/>
+      <c r="I27" s="69"/>
       <c r="J27" s="1"/>
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
@@ -1863,19 +1854,15 @@
       <c r="Y27" s="1"/>
     </row>
     <row r="28" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B28" s="4"/>
-      <c r="C28" s="56"/>
-      <c r="D28" s="57"/>
-      <c r="E28" s="36"/>
-      <c r="F28" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="4"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="57"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="71"/>
+      <c r="C28" s="72"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="71"/>
+      <c r="F28" s="72"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="71"/>
+      <c r="I28" s="72"/>
       <c r="J28" s="1"/>
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
@@ -1894,19 +1881,15 @@
       <c r="Y28" s="1"/>
     </row>
     <row r="29" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="4"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="36"/>
-      <c r="F29" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G29" s="4"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="57"/>
+      <c r="A29" s="70"/>
+      <c r="B29" s="71"/>
+      <c r="C29" s="72"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="71"/>
+      <c r="F29" s="72"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="71"/>
+      <c r="I29" s="72"/>
       <c r="J29" s="1"/>
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
@@ -1925,19 +1908,15 @@
       <c r="Y29" s="1"/>
     </row>
     <row r="30" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B30" s="4"/>
-      <c r="C30" s="56"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="36"/>
-      <c r="F30" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G30" s="4"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="57"/>
+      <c r="A30" s="70"/>
+      <c r="B30" s="71"/>
+      <c r="C30" s="72"/>
+      <c r="D30" s="70"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="72"/>
+      <c r="G30" s="70"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="72"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
@@ -1955,20 +1934,16 @@
       <c r="X30" s="1"/>
       <c r="Y30" s="1"/>
     </row>
-    <row r="31" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="4"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="59"/>
-      <c r="E31" s="36"/>
-      <c r="F31" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G31" s="4"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="59"/>
+    <row r="31" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="70"/>
+      <c r="B31" s="71"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="70"/>
+      <c r="E31" s="71"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="70"/>
+      <c r="H31" s="71"/>
+      <c r="I31" s="72"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
@@ -1986,24 +1961,16 @@
       <c r="X31" s="1"/>
       <c r="Y31" s="1"/>
     </row>
-    <row r="32" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="16"/>
-      <c r="E32" s="36"/>
-      <c r="F32" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" s="29"/>
-      <c r="H32" s="38" t="s">
-        <v>37</v>
-      </c>
-      <c r="I32" s="16"/>
+    <row r="32" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="70"/>
+      <c r="B32" s="71"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="70"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="70"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="72"/>
       <c r="J32" s="1"/>
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
@@ -2021,18 +1988,16 @@
       <c r="X32" s="1"/>
       <c r="Y32" s="1"/>
     </row>
-    <row r="33" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="39"/>
-      <c r="B33" s="19"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="33"/>
-      <c r="F33" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="G33" s="19"/>
-      <c r="H33" s="17"/>
-      <c r="I33" s="19"/>
+    <row r="33" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="70"/>
+      <c r="B33" s="71"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="71"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="70"/>
+      <c r="H33" s="71"/>
+      <c r="I33" s="72"/>
       <c r="J33" s="1"/>
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
@@ -2050,18 +2015,16 @@
       <c r="X33" s="1"/>
       <c r="Y33" s="1"/>
     </row>
-    <row r="34" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="29"/>
+    <row r="34" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="70"/>
+      <c r="B34" s="71"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="70"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="70"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="72"/>
       <c r="J34" s="1"/>
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
@@ -2079,16 +2042,16 @@
       <c r="X34" s="1"/>
       <c r="Y34" s="1"/>
     </row>
-    <row r="35" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="54"/>
-      <c r="B35" s="60"/>
-      <c r="C35" s="55"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="60"/>
-      <c r="F35" s="55"/>
-      <c r="G35" s="54"/>
-      <c r="H35" s="60"/>
-      <c r="I35" s="55"/>
+    <row r="35" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="70"/>
+      <c r="B35" s="71"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="71"/>
+      <c r="I35" s="72"/>
       <c r="J35" s="1"/>
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
@@ -2106,16 +2069,16 @@
       <c r="X35" s="1"/>
       <c r="Y35" s="1"/>
     </row>
-    <row r="36" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="56"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="57"/>
-      <c r="D36" s="56"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="57"/>
-      <c r="G36" s="56"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="57"/>
+    <row r="36" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="70"/>
+      <c r="B36" s="71"/>
+      <c r="C36" s="72"/>
+      <c r="D36" s="70"/>
+      <c r="E36" s="71"/>
+      <c r="F36" s="72"/>
+      <c r="G36" s="70"/>
+      <c r="H36" s="71"/>
+      <c r="I36" s="72"/>
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
@@ -2133,16 +2096,16 @@
       <c r="X36" s="1"/>
       <c r="Y36" s="1"/>
     </row>
-    <row r="37" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="56"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="57"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="57"/>
-      <c r="G37" s="56"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="57"/>
+    <row r="37" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="70"/>
+      <c r="B37" s="71"/>
+      <c r="C37" s="72"/>
+      <c r="D37" s="70"/>
+      <c r="E37" s="71"/>
+      <c r="F37" s="72"/>
+      <c r="G37" s="70"/>
+      <c r="H37" s="71"/>
+      <c r="I37" s="72"/>
       <c r="J37" s="1"/>
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
@@ -2160,16 +2123,16 @@
       <c r="X37" s="1"/>
       <c r="Y37" s="1"/>
     </row>
-    <row r="38" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="56"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="57"/>
-      <c r="G38" s="56"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="57"/>
+    <row r="38" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="70"/>
+      <c r="B38" s="71"/>
+      <c r="C38" s="72"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="71"/>
+      <c r="F38" s="72"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="71"/>
+      <c r="I38" s="72"/>
       <c r="J38" s="1"/>
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
@@ -2188,15 +2151,15 @@
       <c r="Y38" s="1"/>
     </row>
     <row r="39" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="56"/>
-      <c r="B39" s="61"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="56"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="57"/>
-      <c r="G39" s="56"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="57"/>
+      <c r="A39" s="70"/>
+      <c r="B39" s="71"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="70"/>
+      <c r="E39" s="71"/>
+      <c r="F39" s="72"/>
+      <c r="G39" s="70"/>
+      <c r="H39" s="71"/>
+      <c r="I39" s="72"/>
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
@@ -2215,15 +2178,15 @@
       <c r="Y39" s="1"/>
     </row>
     <row r="40" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="56"/>
-      <c r="B40" s="61"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="56"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="57"/>
-      <c r="G40" s="56"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="57"/>
+      <c r="A40" s="70"/>
+      <c r="B40" s="71"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="70"/>
+      <c r="E40" s="71"/>
+      <c r="F40" s="72"/>
+      <c r="G40" s="70"/>
+      <c r="H40" s="71"/>
+      <c r="I40" s="72"/>
       <c r="J40" s="1"/>
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
@@ -2242,15 +2205,15 @@
       <c r="Y40" s="1"/>
     </row>
     <row r="41" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="56"/>
-      <c r="B41" s="61"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="56"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="57"/>
-      <c r="G41" s="56"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="57"/>
+      <c r="A41" s="70"/>
+      <c r="B41" s="71"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="70"/>
+      <c r="E41" s="71"/>
+      <c r="F41" s="72"/>
+      <c r="G41" s="70"/>
+      <c r="H41" s="71"/>
+      <c r="I41" s="72"/>
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
@@ -2269,15 +2232,15 @@
       <c r="Y41" s="1"/>
     </row>
     <row r="42" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="56"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="57"/>
-      <c r="D42" s="56"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="57"/>
-      <c r="G42" s="56"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="57"/>
+      <c r="A42" s="70"/>
+      <c r="B42" s="71"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="70"/>
+      <c r="E42" s="71"/>
+      <c r="F42" s="72"/>
+      <c r="G42" s="70"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="72"/>
       <c r="J42" s="1"/>
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
@@ -2296,15 +2259,15 @@
       <c r="Y42" s="1"/>
     </row>
     <row r="43" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="56"/>
-      <c r="B43" s="61"/>
-      <c r="C43" s="57"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="57"/>
-      <c r="G43" s="56"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="57"/>
+      <c r="A43" s="70"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="70"/>
+      <c r="E43" s="71"/>
+      <c r="F43" s="72"/>
+      <c r="G43" s="70"/>
+      <c r="H43" s="71"/>
+      <c r="I43" s="72"/>
       <c r="J43" s="1"/>
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
@@ -2323,15 +2286,15 @@
       <c r="Y43" s="1"/>
     </row>
     <row r="44" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="56"/>
-      <c r="B44" s="61"/>
-      <c r="C44" s="57"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="57"/>
-      <c r="G44" s="56"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="57"/>
+      <c r="A44" s="70"/>
+      <c r="B44" s="71"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="70"/>
+      <c r="E44" s="71"/>
+      <c r="F44" s="72"/>
+      <c r="G44" s="70"/>
+      <c r="H44" s="71"/>
+      <c r="I44" s="72"/>
       <c r="J44" s="1"/>
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
@@ -2350,15 +2313,15 @@
       <c r="Y44" s="1"/>
     </row>
     <row r="45" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="56"/>
-      <c r="B45" s="61"/>
-      <c r="C45" s="57"/>
-      <c r="D45" s="56"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="57"/>
-      <c r="G45" s="56"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="57"/>
+      <c r="A45" s="70"/>
+      <c r="B45" s="71"/>
+      <c r="C45" s="72"/>
+      <c r="D45" s="70"/>
+      <c r="E45" s="71"/>
+      <c r="F45" s="72"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="71"/>
+      <c r="I45" s="72"/>
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
@@ -2377,15 +2340,15 @@
       <c r="Y45" s="1"/>
     </row>
     <row r="46" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="56"/>
-      <c r="B46" s="61"/>
-      <c r="C46" s="57"/>
-      <c r="D46" s="56"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="57"/>
-      <c r="G46" s="56"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="57"/>
+      <c r="A46" s="70"/>
+      <c r="B46" s="71"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="73"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="75"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="75"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
@@ -2404,15 +2367,21 @@
       <c r="Y46" s="1"/>
     </row>
     <row r="47" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="56"/>
-      <c r="B47" s="61"/>
-      <c r="C47" s="57"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="57"/>
-      <c r="G47" s="56"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="57"/>
+      <c r="A47" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="20"/>
+      <c r="C47" s="21"/>
+      <c r="D47" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="E47" s="20"/>
+      <c r="F47" s="21"/>
+      <c r="G47" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="20"/>
+      <c r="I47" s="21"/>
       <c r="J47" s="1"/>
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
@@ -2431,15 +2400,15 @@
       <c r="Y47" s="1"/>
     </row>
     <row r="48" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="56"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="57"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="57"/>
-      <c r="G48" s="56"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="57"/>
+      <c r="A48" s="67"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="69"/>
+      <c r="D48" s="67"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="69"/>
+      <c r="G48" s="67"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="69"/>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
@@ -2458,15 +2427,15 @@
       <c r="Y48" s="1"/>
     </row>
     <row r="49" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="56"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="57"/>
-      <c r="D49" s="56"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="57"/>
-      <c r="G49" s="56"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="57"/>
+      <c r="A49" s="70"/>
+      <c r="B49" s="71"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="70"/>
+      <c r="E49" s="71"/>
+      <c r="F49" s="72"/>
+      <c r="G49" s="70"/>
+      <c r="H49" s="71"/>
+      <c r="I49" s="72"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
@@ -2485,15 +2454,15 @@
       <c r="Y49" s="1"/>
     </row>
     <row r="50" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="56"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="57"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="57"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="57"/>
+      <c r="A50" s="70"/>
+      <c r="B50" s="71"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="70"/>
+      <c r="E50" s="71"/>
+      <c r="F50" s="72"/>
+      <c r="G50" s="70"/>
+      <c r="H50" s="71"/>
+      <c r="I50" s="72"/>
       <c r="J50" s="1"/>
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
@@ -2512,15 +2481,15 @@
       <c r="Y50" s="1"/>
     </row>
     <row r="51" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="56"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="57"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="57"/>
-      <c r="G51" s="56"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="57"/>
+      <c r="A51" s="70"/>
+      <c r="B51" s="71"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="70"/>
+      <c r="E51" s="71"/>
+      <c r="F51" s="72"/>
+      <c r="G51" s="70"/>
+      <c r="H51" s="71"/>
+      <c r="I51" s="72"/>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -2539,15 +2508,15 @@
       <c r="Y51" s="1"/>
     </row>
     <row r="52" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="56"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="57"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="57"/>
-      <c r="G52" s="56"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="57"/>
+      <c r="A52" s="70"/>
+      <c r="B52" s="71"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="70"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="72"/>
+      <c r="G52" s="70"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="72"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -2566,15 +2535,15 @@
       <c r="Y52" s="1"/>
     </row>
     <row r="53" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="56"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="57"/>
-      <c r="D53" s="56"/>
-      <c r="E53" s="61"/>
-      <c r="F53" s="57"/>
-      <c r="G53" s="56"/>
-      <c r="H53" s="61"/>
-      <c r="I53" s="57"/>
+      <c r="A53" s="70"/>
+      <c r="B53" s="71"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="70"/>
+      <c r="E53" s="71"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="70"/>
+      <c r="H53" s="71"/>
+      <c r="I53" s="72"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
@@ -2593,15 +2562,15 @@
       <c r="Y53" s="1"/>
     </row>
     <row r="54" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="56"/>
-      <c r="B54" s="61"/>
-      <c r="C54" s="57"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="62"/>
-      <c r="F54" s="59"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="62"/>
-      <c r="I54" s="59"/>
+      <c r="A54" s="70"/>
+      <c r="B54" s="71"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="70"/>
+      <c r="E54" s="71"/>
+      <c r="F54" s="72"/>
+      <c r="G54" s="70"/>
+      <c r="H54" s="71"/>
+      <c r="I54" s="72"/>
       <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
@@ -2620,21 +2589,15 @@
       <c r="Y54" s="1"/>
     </row>
     <row r="55" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="43" t="s">
-        <v>40</v>
-      </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="43" t="s">
-        <v>41</v>
-      </c>
-      <c r="E55" s="28"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="43" t="s">
-        <v>42</v>
-      </c>
-      <c r="H55" s="28"/>
-      <c r="I55" s="29"/>
+      <c r="A55" s="70"/>
+      <c r="B55" s="71"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="71"/>
+      <c r="F55" s="72"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="71"/>
+      <c r="I55" s="72"/>
       <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
@@ -2653,15 +2616,15 @@
       <c r="Y55" s="1"/>
     </row>
     <row r="56" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="54"/>
-      <c r="B56" s="60"/>
-      <c r="C56" s="55"/>
-      <c r="D56" s="54"/>
-      <c r="E56" s="60"/>
-      <c r="F56" s="55"/>
-      <c r="G56" s="54"/>
-      <c r="H56" s="60"/>
-      <c r="I56" s="55"/>
+      <c r="A56" s="70"/>
+      <c r="B56" s="71"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="70"/>
+      <c r="E56" s="71"/>
+      <c r="F56" s="72"/>
+      <c r="G56" s="70"/>
+      <c r="H56" s="71"/>
+      <c r="I56" s="72"/>
       <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
@@ -2680,15 +2643,15 @@
       <c r="Y56" s="1"/>
     </row>
     <row r="57" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="56"/>
-      <c r="B57" s="61"/>
-      <c r="C57" s="57"/>
-      <c r="D57" s="56"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="57"/>
-      <c r="G57" s="56"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="57"/>
+      <c r="A57" s="70"/>
+      <c r="B57" s="71"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="73"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="75"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="75"/>
       <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
@@ -2707,15 +2670,15 @@
       <c r="Y57" s="1"/>
     </row>
     <row r="58" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="56"/>
-      <c r="B58" s="61"/>
-      <c r="C58" s="57"/>
-      <c r="D58" s="56"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="57"/>
-      <c r="G58" s="56"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="57"/>
+      <c r="A58" s="70"/>
+      <c r="B58" s="71"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="68"/>
+      <c r="F58" s="69"/>
+      <c r="G58" s="67"/>
+      <c r="H58" s="68"/>
+      <c r="I58" s="69"/>
       <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
@@ -2734,15 +2697,15 @@
       <c r="Y58" s="1"/>
     </row>
     <row r="59" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="56"/>
-      <c r="B59" s="61"/>
-      <c r="C59" s="57"/>
-      <c r="D59" s="56"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="57"/>
-      <c r="G59" s="56"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="57"/>
+      <c r="A59" s="70"/>
+      <c r="B59" s="71"/>
+      <c r="C59" s="72"/>
+      <c r="D59" s="70"/>
+      <c r="E59" s="71"/>
+      <c r="F59" s="72"/>
+      <c r="G59" s="70"/>
+      <c r="H59" s="71"/>
+      <c r="I59" s="72"/>
       <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
@@ -2761,15 +2724,15 @@
       <c r="Y59" s="1"/>
     </row>
     <row r="60" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="56"/>
-      <c r="B60" s="61"/>
-      <c r="C60" s="57"/>
-      <c r="D60" s="56"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="57"/>
-      <c r="G60" s="56"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="57"/>
+      <c r="A60" s="70"/>
+      <c r="B60" s="71"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="70"/>
+      <c r="E60" s="71"/>
+      <c r="F60" s="72"/>
+      <c r="G60" s="70"/>
+      <c r="H60" s="71"/>
+      <c r="I60" s="72"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
@@ -2788,15 +2751,15 @@
       <c r="Y60" s="1"/>
     </row>
     <row r="61" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="56"/>
-      <c r="B61" s="61"/>
-      <c r="C61" s="57"/>
-      <c r="D61" s="56"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="57"/>
-      <c r="G61" s="56"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="57"/>
+      <c r="A61" s="70"/>
+      <c r="B61" s="71"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="70"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="72"/>
+      <c r="G61" s="70"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="72"/>
       <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
@@ -2815,15 +2778,15 @@
       <c r="Y61" s="1"/>
     </row>
     <row r="62" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="56"/>
-      <c r="B62" s="61"/>
-      <c r="C62" s="57"/>
-      <c r="D62" s="56"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="57"/>
-      <c r="G62" s="56"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="57"/>
+      <c r="A62" s="70"/>
+      <c r="B62" s="71"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="70"/>
+      <c r="E62" s="71"/>
+      <c r="F62" s="72"/>
+      <c r="G62" s="70"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="72"/>
       <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
@@ -2842,15 +2805,15 @@
       <c r="Y62" s="1"/>
     </row>
     <row r="63" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="56"/>
-      <c r="B63" s="61"/>
-      <c r="C63" s="57"/>
-      <c r="D63" s="56"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="57"/>
-      <c r="G63" s="56"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="57"/>
+      <c r="A63" s="70"/>
+      <c r="B63" s="71"/>
+      <c r="C63" s="72"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="71"/>
+      <c r="F63" s="72"/>
+      <c r="G63" s="70"/>
+      <c r="H63" s="71"/>
+      <c r="I63" s="72"/>
       <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
@@ -2869,15 +2832,15 @@
       <c r="Y63" s="1"/>
     </row>
     <row r="64" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="56"/>
-      <c r="B64" s="61"/>
-      <c r="C64" s="57"/>
-      <c r="D64" s="56"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="57"/>
-      <c r="G64" s="56"/>
-      <c r="H64" s="61"/>
-      <c r="I64" s="57"/>
+      <c r="A64" s="70"/>
+      <c r="B64" s="71"/>
+      <c r="C64" s="72"/>
+      <c r="D64" s="70"/>
+      <c r="E64" s="71"/>
+      <c r="F64" s="72"/>
+      <c r="G64" s="70"/>
+      <c r="H64" s="71"/>
+      <c r="I64" s="72"/>
       <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
@@ -2896,15 +2859,15 @@
       <c r="Y64" s="1"/>
     </row>
     <row r="65" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="56"/>
-      <c r="B65" s="61"/>
-      <c r="C65" s="57"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="62"/>
-      <c r="F65" s="59"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="62"/>
-      <c r="I65" s="59"/>
+      <c r="A65" s="70"/>
+      <c r="B65" s="71"/>
+      <c r="C65" s="72"/>
+      <c r="D65" s="70"/>
+      <c r="E65" s="71"/>
+      <c r="F65" s="72"/>
+      <c r="G65" s="70"/>
+      <c r="H65" s="71"/>
+      <c r="I65" s="72"/>
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
@@ -2923,15 +2886,15 @@
       <c r="Y65" s="1"/>
     </row>
     <row r="66" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="56"/>
-      <c r="B66" s="61"/>
-      <c r="C66" s="57"/>
-      <c r="D66" s="54"/>
-      <c r="E66" s="60"/>
-      <c r="F66" s="55"/>
-      <c r="G66" s="54"/>
-      <c r="H66" s="60"/>
-      <c r="I66" s="55"/>
+      <c r="A66" s="70"/>
+      <c r="B66" s="71"/>
+      <c r="C66" s="72"/>
+      <c r="D66" s="70"/>
+      <c r="E66" s="71"/>
+      <c r="F66" s="72"/>
+      <c r="G66" s="70"/>
+      <c r="H66" s="71"/>
+      <c r="I66" s="72"/>
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
@@ -2950,15 +2913,15 @@
       <c r="Y66" s="1"/>
     </row>
     <row r="67" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="56"/>
-      <c r="B67" s="61"/>
-      <c r="C67" s="57"/>
-      <c r="D67" s="56"/>
-      <c r="E67" s="61"/>
-      <c r="F67" s="57"/>
-      <c r="G67" s="56"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="57"/>
+      <c r="A67" s="70"/>
+      <c r="B67" s="71"/>
+      <c r="C67" s="72"/>
+      <c r="D67" s="73"/>
+      <c r="E67" s="74"/>
+      <c r="F67" s="75"/>
+      <c r="G67" s="73"/>
+      <c r="H67" s="74"/>
+      <c r="I67" s="75"/>
       <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
@@ -2977,15 +2940,21 @@
       <c r="Y67" s="1"/>
     </row>
     <row r="68" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="56"/>
-      <c r="B68" s="61"/>
-      <c r="C68" s="57"/>
-      <c r="D68" s="56"/>
-      <c r="E68" s="61"/>
-      <c r="F68" s="57"/>
-      <c r="G68" s="56"/>
-      <c r="H68" s="61"/>
-      <c r="I68" s="57"/>
+      <c r="A68" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B68" s="20"/>
+      <c r="C68" s="21"/>
+      <c r="D68" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="E68" s="20"/>
+      <c r="F68" s="21"/>
+      <c r="G68" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="H68" s="20"/>
+      <c r="I68" s="21"/>
       <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
@@ -3004,15 +2973,15 @@
       <c r="Y68" s="1"/>
     </row>
     <row r="69" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="56"/>
-      <c r="B69" s="61"/>
-      <c r="C69" s="57"/>
-      <c r="D69" s="56"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="57"/>
-      <c r="G69" s="56"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="57"/>
+      <c r="A69" s="67"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="67"/>
+      <c r="E69" s="68"/>
+      <c r="F69" s="69"/>
+      <c r="G69" s="76"/>
+      <c r="H69" s="68"/>
+      <c r="I69" s="69"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
@@ -3031,15 +3000,15 @@
       <c r="Y69" s="1"/>
     </row>
     <row r="70" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="56"/>
-      <c r="B70" s="61"/>
-      <c r="C70" s="57"/>
-      <c r="D70" s="56"/>
-      <c r="E70" s="61"/>
-      <c r="F70" s="57"/>
-      <c r="G70" s="56"/>
-      <c r="H70" s="61"/>
-      <c r="I70" s="57"/>
+      <c r="A70" s="70"/>
+      <c r="B70" s="71"/>
+      <c r="C70" s="72"/>
+      <c r="D70" s="70"/>
+      <c r="E70" s="71"/>
+      <c r="F70" s="72"/>
+      <c r="G70" s="70"/>
+      <c r="H70" s="71"/>
+      <c r="I70" s="72"/>
       <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
@@ -3058,15 +3027,15 @@
       <c r="Y70" s="1"/>
     </row>
     <row r="71" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="56"/>
-      <c r="B71" s="61"/>
-      <c r="C71" s="57"/>
-      <c r="D71" s="56"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="57"/>
-      <c r="G71" s="56"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="57"/>
+      <c r="A71" s="70"/>
+      <c r="B71" s="71"/>
+      <c r="C71" s="72"/>
+      <c r="D71" s="70"/>
+      <c r="E71" s="71"/>
+      <c r="F71" s="72"/>
+      <c r="G71" s="70"/>
+      <c r="H71" s="71"/>
+      <c r="I71" s="72"/>
       <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
@@ -3085,15 +3054,15 @@
       <c r="Y71" s="1"/>
     </row>
     <row r="72" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="56"/>
-      <c r="B72" s="61"/>
-      <c r="C72" s="57"/>
-      <c r="D72" s="56"/>
-      <c r="E72" s="61"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="56"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="57"/>
+      <c r="A72" s="70"/>
+      <c r="B72" s="71"/>
+      <c r="C72" s="72"/>
+      <c r="D72" s="70"/>
+      <c r="E72" s="71"/>
+      <c r="F72" s="72"/>
+      <c r="G72" s="70"/>
+      <c r="H72" s="71"/>
+      <c r="I72" s="72"/>
       <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
@@ -3112,15 +3081,15 @@
       <c r="Y72" s="1"/>
     </row>
     <row r="73" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="56"/>
-      <c r="B73" s="61"/>
-      <c r="C73" s="57"/>
-      <c r="D73" s="56"/>
-      <c r="E73" s="61"/>
-      <c r="F73" s="57"/>
-      <c r="G73" s="56"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="57"/>
+      <c r="A73" s="70"/>
+      <c r="B73" s="71"/>
+      <c r="C73" s="72"/>
+      <c r="D73" s="70"/>
+      <c r="E73" s="71"/>
+      <c r="F73" s="72"/>
+      <c r="G73" s="70"/>
+      <c r="H73" s="71"/>
+      <c r="I73" s="72"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
@@ -3139,15 +3108,15 @@
       <c r="Y73" s="1"/>
     </row>
     <row r="74" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="56"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="57"/>
-      <c r="D74" s="56"/>
-      <c r="E74" s="61"/>
-      <c r="F74" s="57"/>
-      <c r="G74" s="56"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="57"/>
+      <c r="A74" s="70"/>
+      <c r="B74" s="71"/>
+      <c r="C74" s="72"/>
+      <c r="D74" s="70"/>
+      <c r="E74" s="71"/>
+      <c r="F74" s="72"/>
+      <c r="G74" s="70"/>
+      <c r="H74" s="71"/>
+      <c r="I74" s="72"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
@@ -3166,15 +3135,15 @@
       <c r="Y74" s="1"/>
     </row>
     <row r="75" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="56"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="57"/>
-      <c r="D75" s="58"/>
-      <c r="E75" s="62"/>
-      <c r="F75" s="59"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="62"/>
-      <c r="I75" s="59"/>
+      <c r="A75" s="70"/>
+      <c r="B75" s="71"/>
+      <c r="C75" s="72"/>
+      <c r="D75" s="70"/>
+      <c r="E75" s="71"/>
+      <c r="F75" s="72"/>
+      <c r="G75" s="70"/>
+      <c r="H75" s="71"/>
+      <c r="I75" s="72"/>
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
@@ -3193,21 +3162,15 @@
       <c r="Y75" s="1"/>
     </row>
     <row r="76" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="43" t="s">
-        <v>43</v>
-      </c>
-      <c r="B76" s="28"/>
-      <c r="C76" s="29"/>
-      <c r="D76" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="E76" s="28"/>
-      <c r="F76" s="29"/>
-      <c r="G76" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="H76" s="28"/>
-      <c r="I76" s="29"/>
+      <c r="A76" s="70"/>
+      <c r="B76" s="71"/>
+      <c r="C76" s="72"/>
+      <c r="D76" s="70"/>
+      <c r="E76" s="71"/>
+      <c r="F76" s="72"/>
+      <c r="G76" s="70"/>
+      <c r="H76" s="71"/>
+      <c r="I76" s="72"/>
       <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
@@ -3226,15 +3189,15 @@
       <c r="Y76" s="1"/>
     </row>
     <row r="77" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="54"/>
-      <c r="B77" s="60"/>
-      <c r="C77" s="55"/>
-      <c r="D77" s="54"/>
-      <c r="E77" s="60"/>
-      <c r="F77" s="55"/>
-      <c r="G77" s="63"/>
-      <c r="H77" s="60"/>
-      <c r="I77" s="55"/>
+      <c r="A77" s="70"/>
+      <c r="B77" s="71"/>
+      <c r="C77" s="72"/>
+      <c r="D77" s="70"/>
+      <c r="E77" s="71"/>
+      <c r="F77" s="72"/>
+      <c r="G77" s="70"/>
+      <c r="H77" s="71"/>
+      <c r="I77" s="72"/>
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
@@ -3253,15 +3216,15 @@
       <c r="Y77" s="1"/>
     </row>
     <row r="78" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="56"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="57"/>
-      <c r="D78" s="56"/>
-      <c r="E78" s="61"/>
-      <c r="F78" s="57"/>
-      <c r="G78" s="56"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="57"/>
+      <c r="A78" s="70"/>
+      <c r="B78" s="71"/>
+      <c r="C78" s="72"/>
+      <c r="D78" s="73"/>
+      <c r="E78" s="74"/>
+      <c r="F78" s="75"/>
+      <c r="G78" s="73"/>
+      <c r="H78" s="74"/>
+      <c r="I78" s="75"/>
       <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
@@ -3280,15 +3243,15 @@
       <c r="Y78" s="1"/>
     </row>
     <row r="79" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="56"/>
-      <c r="B79" s="61"/>
-      <c r="C79" s="57"/>
-      <c r="D79" s="56"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="57"/>
-      <c r="G79" s="56"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="57"/>
+      <c r="A79" s="70"/>
+      <c r="B79" s="71"/>
+      <c r="C79" s="72"/>
+      <c r="D79" s="67"/>
+      <c r="E79" s="68"/>
+      <c r="F79" s="69"/>
+      <c r="G79" s="67"/>
+      <c r="H79" s="68"/>
+      <c r="I79" s="69"/>
       <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
@@ -3307,15 +3270,15 @@
       <c r="Y79" s="1"/>
     </row>
     <row r="80" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="56"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="57"/>
-      <c r="D80" s="56"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="57"/>
-      <c r="G80" s="56"/>
-      <c r="H80" s="61"/>
-      <c r="I80" s="57"/>
+      <c r="A80" s="70"/>
+      <c r="B80" s="71"/>
+      <c r="C80" s="72"/>
+      <c r="D80" s="70"/>
+      <c r="E80" s="71"/>
+      <c r="F80" s="72"/>
+      <c r="G80" s="70"/>
+      <c r="H80" s="71"/>
+      <c r="I80" s="72"/>
       <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
@@ -3334,15 +3297,15 @@
       <c r="Y80" s="1"/>
     </row>
     <row r="81" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="56"/>
-      <c r="B81" s="61"/>
-      <c r="C81" s="57"/>
-      <c r="D81" s="56"/>
-      <c r="E81" s="61"/>
-      <c r="F81" s="57"/>
-      <c r="G81" s="56"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="57"/>
+      <c r="A81" s="70"/>
+      <c r="B81" s="71"/>
+      <c r="C81" s="72"/>
+      <c r="D81" s="70"/>
+      <c r="E81" s="71"/>
+      <c r="F81" s="72"/>
+      <c r="G81" s="70"/>
+      <c r="H81" s="71"/>
+      <c r="I81" s="72"/>
       <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
@@ -3361,15 +3324,15 @@
       <c r="Y81" s="1"/>
     </row>
     <row r="82" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="56"/>
-      <c r="B82" s="61"/>
-      <c r="C82" s="57"/>
-      <c r="D82" s="56"/>
-      <c r="E82" s="61"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="56"/>
-      <c r="H82" s="61"/>
-      <c r="I82" s="57"/>
+      <c r="A82" s="70"/>
+      <c r="B82" s="71"/>
+      <c r="C82" s="72"/>
+      <c r="D82" s="70"/>
+      <c r="E82" s="71"/>
+      <c r="F82" s="72"/>
+      <c r="G82" s="70"/>
+      <c r="H82" s="71"/>
+      <c r="I82" s="72"/>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
@@ -3388,15 +3351,15 @@
       <c r="Y82" s="1"/>
     </row>
     <row r="83" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="56"/>
-      <c r="B83" s="61"/>
-      <c r="C83" s="57"/>
-      <c r="D83" s="56"/>
-      <c r="E83" s="61"/>
-      <c r="F83" s="57"/>
-      <c r="G83" s="56"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="57"/>
+      <c r="A83" s="70"/>
+      <c r="B83" s="71"/>
+      <c r="C83" s="72"/>
+      <c r="D83" s="70"/>
+      <c r="E83" s="71"/>
+      <c r="F83" s="72"/>
+      <c r="G83" s="70"/>
+      <c r="H83" s="71"/>
+      <c r="I83" s="72"/>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
@@ -3415,15 +3378,15 @@
       <c r="Y83" s="1"/>
     </row>
     <row r="84" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="56"/>
-      <c r="B84" s="61"/>
-      <c r="C84" s="57"/>
-      <c r="D84" s="56"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="56"/>
-      <c r="H84" s="61"/>
-      <c r="I84" s="57"/>
+      <c r="A84" s="70"/>
+      <c r="B84" s="71"/>
+      <c r="C84" s="72"/>
+      <c r="D84" s="70"/>
+      <c r="E84" s="71"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="70"/>
+      <c r="H84" s="71"/>
+      <c r="I84" s="72"/>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
@@ -3442,15 +3405,15 @@
       <c r="Y84" s="1"/>
     </row>
     <row r="85" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="56"/>
-      <c r="B85" s="61"/>
-      <c r="C85" s="57"/>
-      <c r="D85" s="56"/>
-      <c r="E85" s="61"/>
-      <c r="F85" s="57"/>
-      <c r="G85" s="56"/>
-      <c r="H85" s="61"/>
-      <c r="I85" s="57"/>
+      <c r="A85" s="70"/>
+      <c r="B85" s="71"/>
+      <c r="C85" s="72"/>
+      <c r="D85" s="70"/>
+      <c r="E85" s="71"/>
+      <c r="F85" s="72"/>
+      <c r="G85" s="70"/>
+      <c r="H85" s="71"/>
+      <c r="I85" s="72"/>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
@@ -3469,15 +3432,15 @@
       <c r="Y85" s="1"/>
     </row>
     <row r="86" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="56"/>
-      <c r="B86" s="61"/>
-      <c r="C86" s="57"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="62"/>
-      <c r="F86" s="59"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="62"/>
-      <c r="I86" s="59"/>
+      <c r="A86" s="70"/>
+      <c r="B86" s="71"/>
+      <c r="C86" s="72"/>
+      <c r="D86" s="70"/>
+      <c r="E86" s="71"/>
+      <c r="F86" s="72"/>
+      <c r="G86" s="70"/>
+      <c r="H86" s="71"/>
+      <c r="I86" s="72"/>
       <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
@@ -3496,15 +3459,15 @@
       <c r="Y86" s="1"/>
     </row>
     <row r="87" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="56"/>
-      <c r="B87" s="61"/>
-      <c r="C87" s="57"/>
-      <c r="D87" s="54"/>
-      <c r="E87" s="60"/>
-      <c r="F87" s="55"/>
-      <c r="G87" s="54"/>
-      <c r="H87" s="60"/>
-      <c r="I87" s="55"/>
+      <c r="A87" s="70"/>
+      <c r="B87" s="71"/>
+      <c r="C87" s="72"/>
+      <c r="D87" s="70"/>
+      <c r="E87" s="71"/>
+      <c r="F87" s="72"/>
+      <c r="G87" s="70"/>
+      <c r="H87" s="71"/>
+      <c r="I87" s="72"/>
       <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
@@ -3523,15 +3486,15 @@
       <c r="Y87" s="1"/>
     </row>
     <row r="88" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="56"/>
-      <c r="B88" s="61"/>
-      <c r="C88" s="57"/>
-      <c r="D88" s="56"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="57"/>
-      <c r="G88" s="56"/>
-      <c r="H88" s="61"/>
-      <c r="I88" s="57"/>
+      <c r="A88" s="73"/>
+      <c r="B88" s="74"/>
+      <c r="C88" s="75"/>
+      <c r="D88" s="73"/>
+      <c r="E88" s="74"/>
+      <c r="F88" s="75"/>
+      <c r="G88" s="73"/>
+      <c r="H88" s="74"/>
+      <c r="I88" s="75"/>
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
@@ -3550,15 +3513,21 @@
       <c r="Y88" s="1"/>
     </row>
     <row r="89" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="56"/>
-      <c r="B89" s="61"/>
-      <c r="C89" s="57"/>
-      <c r="D89" s="56"/>
-      <c r="E89" s="61"/>
-      <c r="F89" s="57"/>
-      <c r="G89" s="56"/>
-      <c r="H89" s="61"/>
-      <c r="I89" s="57"/>
+      <c r="A89" s="31" t="s">
+        <v>37</v>
+      </c>
+      <c r="B89" s="20"/>
+      <c r="C89" s="21"/>
+      <c r="D89" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="E89" s="20"/>
+      <c r="F89" s="21"/>
+      <c r="G89" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H89" s="20"/>
+      <c r="I89" s="21"/>
       <c r="J89" s="1"/>
       <c r="K89" s="1"/>
       <c r="L89" s="1"/>
@@ -3577,15 +3546,15 @@
       <c r="Y89" s="1"/>
     </row>
     <row r="90" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="56"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="57"/>
-      <c r="D90" s="56"/>
-      <c r="E90" s="61"/>
-      <c r="F90" s="57"/>
-      <c r="G90" s="56"/>
-      <c r="H90" s="61"/>
-      <c r="I90" s="57"/>
+      <c r="A90" s="32"/>
+      <c r="B90" s="33"/>
+      <c r="C90" s="33"/>
+      <c r="D90" s="33"/>
+      <c r="E90" s="33"/>
+      <c r="F90" s="33"/>
+      <c r="G90" s="33"/>
+      <c r="H90" s="33"/>
+      <c r="I90" s="8"/>
       <c r="J90" s="1"/>
       <c r="K90" s="1"/>
       <c r="L90" s="1"/>
@@ -3604,15 +3573,19 @@
       <c r="Y90" s="1"/>
     </row>
     <row r="91" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="56"/>
-      <c r="B91" s="61"/>
-      <c r="C91" s="57"/>
-      <c r="D91" s="56"/>
-      <c r="E91" s="61"/>
-      <c r="F91" s="57"/>
-      <c r="G91" s="56"/>
-      <c r="H91" s="61"/>
-      <c r="I91" s="57"/>
+      <c r="A91" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="B91" s="20"/>
+      <c r="C91" s="21"/>
+      <c r="D91" s="32"/>
+      <c r="E91" s="8"/>
+      <c r="F91" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="G91" s="20"/>
+      <c r="H91" s="20"/>
+      <c r="I91" s="21"/>
       <c r="J91" s="1"/>
       <c r="K91" s="1"/>
       <c r="L91" s="1"/>
@@ -3631,15 +3604,25 @@
       <c r="Y91" s="1"/>
     </row>
     <row r="92" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="56"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="57"/>
-      <c r="D92" s="56"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="57"/>
-      <c r="G92" s="56"/>
-      <c r="H92" s="61"/>
-      <c r="I92" s="57"/>
+      <c r="A92" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C92" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="D92" s="33"/>
+      <c r="E92" s="8"/>
+      <c r="F92" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="G92" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="H92" s="20"/>
+      <c r="I92" s="21"/>
       <c r="J92" s="1"/>
       <c r="K92" s="1"/>
       <c r="L92" s="1"/>
@@ -3658,15 +3641,17 @@
       <c r="Y92" s="1"/>
     </row>
     <row r="93" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="56"/>
-      <c r="B93" s="61"/>
-      <c r="C93" s="57"/>
-      <c r="D93" s="56"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="57"/>
-      <c r="G93" s="56"/>
-      <c r="H93" s="61"/>
-      <c r="I93" s="57"/>
+      <c r="A93" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="B93" s="11"/>
+      <c r="C93" s="11"/>
+      <c r="D93" s="33"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="20"/>
+      <c r="I93" s="21"/>
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
@@ -3685,15 +3670,17 @@
       <c r="Y93" s="1"/>
     </row>
     <row r="94" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="56"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="57"/>
-      <c r="D94" s="56"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="57"/>
-      <c r="G94" s="56"/>
-      <c r="H94" s="61"/>
-      <c r="I94" s="57"/>
+      <c r="A94" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="33"/>
+      <c r="E94" s="8"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="35"/>
+      <c r="H94" s="20"/>
+      <c r="I94" s="21"/>
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
@@ -3712,15 +3699,17 @@
       <c r="Y94" s="1"/>
     </row>
     <row r="95" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="56"/>
-      <c r="B95" s="61"/>
-      <c r="C95" s="57"/>
-      <c r="D95" s="56"/>
-      <c r="E95" s="61"/>
-      <c r="F95" s="57"/>
-      <c r="G95" s="56"/>
-      <c r="H95" s="61"/>
-      <c r="I95" s="57"/>
+      <c r="A95" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="33"/>
+      <c r="E95" s="8"/>
+      <c r="F95" s="4"/>
+      <c r="G95" s="28"/>
+      <c r="H95" s="20"/>
+      <c r="I95" s="21"/>
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
@@ -3739,15 +3728,17 @@
       <c r="Y95" s="1"/>
     </row>
     <row r="96" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="58"/>
-      <c r="B96" s="62"/>
-      <c r="C96" s="59"/>
-      <c r="D96" s="58"/>
-      <c r="E96" s="62"/>
-      <c r="F96" s="59"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="62"/>
-      <c r="I96" s="59"/>
+      <c r="A96" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="33"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="4"/>
+      <c r="G96" s="28"/>
+      <c r="H96" s="20"/>
+      <c r="I96" s="21"/>
       <c r="J96" s="1"/>
       <c r="K96" s="1"/>
       <c r="L96" s="1"/>
@@ -3766,21 +3757,17 @@
       <c r="Y96" s="1"/>
     </row>
     <row r="97" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B97" s="28"/>
-      <c r="C97" s="29"/>
-      <c r="D97" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="E97" s="28"/>
-      <c r="F97" s="29"/>
-      <c r="G97" s="43" t="s">
+      <c r="A97" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H97" s="28"/>
-      <c r="I97" s="29"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="33"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="4"/>
+      <c r="G97" s="28"/>
+      <c r="H97" s="20"/>
+      <c r="I97" s="21"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
@@ -3799,15 +3786,17 @@
       <c r="Y97" s="1"/>
     </row>
     <row r="98" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="45"/>
-      <c r="B98" s="42"/>
-      <c r="C98" s="42"/>
-      <c r="D98" s="42"/>
-      <c r="E98" s="42"/>
-      <c r="F98" s="42"/>
-      <c r="G98" s="42"/>
-      <c r="H98" s="42"/>
-      <c r="I98" s="9"/>
+      <c r="A98" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="33"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="4"/>
+      <c r="G98" s="28"/>
+      <c r="H98" s="20"/>
+      <c r="I98" s="21"/>
       <c r="J98" s="1"/>
       <c r="K98" s="1"/>
       <c r="L98" s="1"/>
@@ -3826,19 +3815,17 @@
       <c r="Y98" s="1"/>
     </row>
     <row r="99" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="46" t="s">
-        <v>48</v>
+      <c r="A99" s="10" t="s">
+        <v>50</v>
       </c>
-      <c r="B99" s="28"/>
-      <c r="C99" s="29"/>
-      <c r="D99" s="45"/>
-      <c r="E99" s="9"/>
-      <c r="F99" s="46" t="s">
-        <v>49</v>
-      </c>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="33"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="4"/>
       <c r="G99" s="28"/>
-      <c r="H99" s="28"/>
-      <c r="I99" s="29"/>
+      <c r="H99" s="20"/>
+      <c r="I99" s="21"/>
       <c r="J99" s="1"/>
       <c r="K99" s="1"/>
       <c r="L99" s="1"/>
@@ -3858,24 +3845,16 @@
     </row>
     <row r="100" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="B100" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C100" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="D100" s="42"/>
-      <c r="E100" s="9"/>
-      <c r="F100" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" s="47" t="s">
-        <v>52</v>
-      </c>
-      <c r="H100" s="28"/>
-      <c r="I100" s="29"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="4"/>
+      <c r="G100" s="28"/>
+      <c r="H100" s="20"/>
+      <c r="I100" s="21"/>
       <c r="J100" s="1"/>
       <c r="K100" s="1"/>
       <c r="L100" s="1"/>
@@ -3894,17 +3873,17 @@
       <c r="Y100" s="1"/>
     </row>
     <row r="101" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="11" t="s">
-        <v>53</v>
+      <c r="A101" s="10" t="s">
+        <v>52</v>
       </c>
-      <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="42"/>
-      <c r="E101" s="9"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="48"/>
-      <c r="H101" s="28"/>
-      <c r="I101" s="29"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="4"/>
+      <c r="G101" s="28"/>
+      <c r="H101" s="20"/>
+      <c r="I101" s="21"/>
       <c r="J101" s="1"/>
       <c r="K101" s="1"/>
       <c r="L101" s="1"/>
@@ -3923,17 +3902,17 @@
       <c r="Y101" s="1"/>
     </row>
     <row r="102" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="11" t="s">
-        <v>54</v>
+      <c r="A102" s="10" t="s">
+        <v>53</v>
       </c>
-      <c r="B102" s="12"/>
-      <c r="C102" s="12"/>
-      <c r="D102" s="42"/>
-      <c r="E102" s="9"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="48"/>
-      <c r="H102" s="28"/>
-      <c r="I102" s="29"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="7"/>
+      <c r="E102" s="8"/>
+      <c r="F102" s="77"/>
+      <c r="G102" s="28"/>
+      <c r="H102" s="20"/>
+      <c r="I102" s="21"/>
       <c r="J102" s="1"/>
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
@@ -3952,17 +3931,15 @@
       <c r="Y102" s="1"/>
     </row>
     <row r="103" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="B103" s="12"/>
-      <c r="C103" s="12"/>
-      <c r="D103" s="42"/>
-      <c r="E103" s="9"/>
-      <c r="F103" s="4"/>
-      <c r="G103" s="30"/>
-      <c r="H103" s="28"/>
-      <c r="I103" s="29"/>
+      <c r="A103" s="8"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="8"/>
+      <c r="F103" s="8"/>
+      <c r="G103" s="8"/>
+      <c r="H103" s="8"/>
+      <c r="I103" s="8"/>
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
@@ -3981,17 +3958,17 @@
       <c r="Y103" s="1"/>
     </row>
     <row r="104" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="11" t="s">
-        <v>56</v>
+      <c r="A104" s="29" t="s">
+        <v>54</v>
       </c>
-      <c r="B104" s="12"/>
-      <c r="C104" s="12"/>
-      <c r="D104" s="42"/>
-      <c r="E104" s="9"/>
-      <c r="F104" s="4"/>
-      <c r="G104" s="30"/>
-      <c r="H104" s="28"/>
-      <c r="I104" s="29"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="23"/>
+      <c r="D104" s="23"/>
+      <c r="E104" s="23"/>
+      <c r="F104" s="23"/>
+      <c r="G104" s="23"/>
+      <c r="H104" s="23"/>
+      <c r="I104" s="24"/>
       <c r="J104" s="1"/>
       <c r="K104" s="1"/>
       <c r="L104" s="1"/>
@@ -4010,17 +3987,23 @@
       <c r="Y104" s="1"/>
     </row>
     <row r="105" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="11" t="s">
+      <c r="A105" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B105" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="C105" s="20"/>
+      <c r="D105" s="20"/>
+      <c r="E105" s="20"/>
+      <c r="F105" s="20"/>
+      <c r="G105" s="21"/>
+      <c r="H105" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B105" s="12"/>
-      <c r="C105" s="12"/>
-      <c r="D105" s="42"/>
-      <c r="E105" s="9"/>
-      <c r="F105" s="4"/>
-      <c r="G105" s="30"/>
-      <c r="H105" s="28"/>
-      <c r="I105" s="29"/>
+      <c r="I105" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="J105" s="1"/>
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
@@ -4039,17 +4022,19 @@
       <c r="Y105" s="1"/>
     </row>
     <row r="106" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="11" t="s">
-        <v>58</v>
+      <c r="A106" s="12">
+        <v>1</v>
       </c>
-      <c r="B106" s="12"/>
-      <c r="C106" s="12"/>
-      <c r="D106" s="42"/>
-      <c r="E106" s="9"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="30"/>
-      <c r="H106" s="28"/>
-      <c r="I106" s="29"/>
+      <c r="B106" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C106" s="20"/>
+      <c r="D106" s="20"/>
+      <c r="E106" s="20"/>
+      <c r="F106" s="20"/>
+      <c r="G106" s="21"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
@@ -4068,17 +4053,19 @@
       <c r="Y106" s="1"/>
     </row>
     <row r="107" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="11" t="s">
-        <v>59</v>
+      <c r="A107" s="12">
+        <v>2</v>
       </c>
-      <c r="B107" s="12"/>
-      <c r="C107" s="12"/>
-      <c r="D107" s="42"/>
-      <c r="E107" s="9"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="30"/>
-      <c r="H107" s="28"/>
-      <c r="I107" s="29"/>
+      <c r="B107" s="26" t="s">
+        <v>60</v>
+      </c>
+      <c r="C107" s="20"/>
+      <c r="D107" s="20"/>
+      <c r="E107" s="20"/>
+      <c r="F107" s="20"/>
+      <c r="G107" s="21"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
       <c r="J107" s="1"/>
       <c r="K107" s="1"/>
       <c r="L107" s="1"/>
@@ -4097,17 +4084,19 @@
       <c r="Y107" s="1"/>
     </row>
     <row r="108" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="11" t="s">
-        <v>60</v>
+      <c r="A108" s="12">
+        <v>3</v>
       </c>
-      <c r="B108" s="12"/>
-      <c r="C108" s="12"/>
-      <c r="D108" s="8"/>
-      <c r="E108" s="9"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="30"/>
-      <c r="H108" s="28"/>
-      <c r="I108" s="29"/>
+      <c r="B108" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="C108" s="20"/>
+      <c r="D108" s="20"/>
+      <c r="E108" s="20"/>
+      <c r="F108" s="20"/>
+      <c r="G108" s="21"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
@@ -4126,17 +4115,19 @@
       <c r="Y108" s="1"/>
     </row>
     <row r="109" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="11" t="s">
-        <v>61</v>
+      <c r="A109" s="12">
+        <v>4</v>
       </c>
-      <c r="B109" s="12"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="8"/>
-      <c r="E109" s="9"/>
-      <c r="F109" s="4"/>
-      <c r="G109" s="30"/>
-      <c r="H109" s="28"/>
-      <c r="I109" s="29"/>
+      <c r="B109" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C109" s="20"/>
+      <c r="D109" s="20"/>
+      <c r="E109" s="20"/>
+      <c r="F109" s="20"/>
+      <c r="G109" s="21"/>
+      <c r="H109" s="4"/>
+      <c r="I109" s="4"/>
       <c r="J109" s="1"/>
       <c r="K109" s="1"/>
       <c r="L109" s="1"/>
@@ -4155,17 +4146,19 @@
       <c r="Y109" s="1"/>
     </row>
     <row r="110" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="11" t="s">
-        <v>62</v>
+      <c r="A110" s="12">
+        <v>5</v>
       </c>
-      <c r="B110" s="12"/>
-      <c r="C110" s="12"/>
-      <c r="D110" s="8"/>
-      <c r="E110" s="9"/>
-      <c r="F110" s="6"/>
-      <c r="G110" s="30"/>
-      <c r="H110" s="28"/>
-      <c r="I110" s="29"/>
+      <c r="B110" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C110" s="20"/>
+      <c r="D110" s="20"/>
+      <c r="E110" s="20"/>
+      <c r="F110" s="20"/>
+      <c r="G110" s="21"/>
+      <c r="H110" s="4"/>
+      <c r="I110" s="4"/>
       <c r="J110" s="1"/>
       <c r="K110" s="1"/>
       <c r="L110" s="1"/>
@@ -4184,15 +4177,19 @@
       <c r="Y110" s="1"/>
     </row>
     <row r="111" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="9"/>
-      <c r="B111" s="9"/>
-      <c r="C111" s="9"/>
-      <c r="D111" s="9"/>
-      <c r="E111" s="9"/>
-      <c r="F111" s="9"/>
-      <c r="G111" s="9"/>
-      <c r="H111" s="9"/>
-      <c r="I111" s="9"/>
+      <c r="A111" s="12">
+        <v>6</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="C111" s="20"/>
+      <c r="D111" s="20"/>
+      <c r="E111" s="20"/>
+      <c r="F111" s="20"/>
+      <c r="G111" s="21"/>
+      <c r="H111" s="4"/>
+      <c r="I111" s="4"/>
       <c r="J111" s="1"/>
       <c r="K111" s="1"/>
       <c r="L111" s="1"/>
@@ -4211,17 +4208,19 @@
       <c r="Y111" s="1"/>
     </row>
     <row r="112" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="49" t="s">
-        <v>63</v>
+      <c r="A112" s="12">
+        <v>7</v>
       </c>
-      <c r="B112" s="15"/>
-      <c r="C112" s="15"/>
-      <c r="D112" s="15"/>
-      <c r="E112" s="15"/>
-      <c r="F112" s="15"/>
-      <c r="G112" s="15"/>
-      <c r="H112" s="15"/>
-      <c r="I112" s="16"/>
+      <c r="B112" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="C112" s="20"/>
+      <c r="D112" s="20"/>
+      <c r="E112" s="20"/>
+      <c r="F112" s="20"/>
+      <c r="G112" s="21"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
       <c r="J112" s="1"/>
       <c r="K112" s="1"/>
       <c r="L112" s="1"/>
@@ -4240,23 +4239,19 @@
       <c r="Y112" s="1"/>
     </row>
     <row r="113" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="10" t="s">
-        <v>64</v>
+      <c r="A113" s="12">
+        <v>8</v>
       </c>
-      <c r="B113" s="47" t="s">
-        <v>65</v>
-      </c>
-      <c r="C113" s="28"/>
-      <c r="D113" s="28"/>
-      <c r="E113" s="28"/>
-      <c r="F113" s="28"/>
-      <c r="G113" s="29"/>
-      <c r="H113" s="3" t="s">
+      <c r="B113" s="26" t="s">
         <v>66</v>
       </c>
-      <c r="I113" s="3" t="s">
-        <v>67</v>
-      </c>
+      <c r="C113" s="20"/>
+      <c r="D113" s="20"/>
+      <c r="E113" s="20"/>
+      <c r="F113" s="20"/>
+      <c r="G113" s="21"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
       <c r="J113" s="1"/>
       <c r="K113" s="1"/>
       <c r="L113" s="1"/>
@@ -4275,17 +4270,17 @@
       <c r="Y113" s="1"/>
     </row>
     <row r="114" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="13">
-        <v>1</v>
+      <c r="A114" s="12">
+        <v>9</v>
       </c>
-      <c r="B114" s="50" t="s">
-        <v>68</v>
+      <c r="B114" s="26" t="s">
+        <v>67</v>
       </c>
-      <c r="C114" s="28"/>
-      <c r="D114" s="28"/>
-      <c r="E114" s="28"/>
-      <c r="F114" s="28"/>
-      <c r="G114" s="29"/>
+      <c r="C114" s="20"/>
+      <c r="D114" s="20"/>
+      <c r="E114" s="20"/>
+      <c r="F114" s="20"/>
+      <c r="G114" s="21"/>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
       <c r="J114" s="1"/>
@@ -4306,17 +4301,17 @@
       <c r="Y114" s="1"/>
     </row>
     <row r="115" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="13">
-        <v>2</v>
+      <c r="A115" s="12">
+        <v>10</v>
       </c>
-      <c r="B115" s="50" t="s">
-        <v>69</v>
+      <c r="B115" s="26" t="s">
+        <v>68</v>
       </c>
-      <c r="C115" s="28"/>
-      <c r="D115" s="28"/>
-      <c r="E115" s="28"/>
-      <c r="F115" s="28"/>
-      <c r="G115" s="29"/>
+      <c r="C115" s="20"/>
+      <c r="D115" s="20"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="20"/>
+      <c r="G115" s="21"/>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
       <c r="J115" s="1"/>
@@ -4337,17 +4332,17 @@
       <c r="Y115" s="1"/>
     </row>
     <row r="116" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="13">
-        <v>3</v>
+      <c r="A116" s="12">
+        <v>11</v>
       </c>
-      <c r="B116" s="50" t="s">
-        <v>70</v>
+      <c r="B116" s="26" t="s">
+        <v>69</v>
       </c>
-      <c r="C116" s="28"/>
-      <c r="D116" s="28"/>
-      <c r="E116" s="28"/>
-      <c r="F116" s="28"/>
-      <c r="G116" s="29"/>
+      <c r="C116" s="20"/>
+      <c r="D116" s="20"/>
+      <c r="E116" s="20"/>
+      <c r="F116" s="20"/>
+      <c r="G116" s="21"/>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
       <c r="J116" s="1"/>
@@ -4368,17 +4363,17 @@
       <c r="Y116" s="1"/>
     </row>
     <row r="117" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="13">
-        <v>4</v>
+      <c r="A117" s="12">
+        <v>12</v>
       </c>
-      <c r="B117" s="50" t="s">
-        <v>71</v>
+      <c r="B117" s="26" t="s">
+        <v>70</v>
       </c>
-      <c r="C117" s="28"/>
-      <c r="D117" s="28"/>
-      <c r="E117" s="28"/>
-      <c r="F117" s="28"/>
-      <c r="G117" s="29"/>
+      <c r="C117" s="20"/>
+      <c r="D117" s="20"/>
+      <c r="E117" s="20"/>
+      <c r="F117" s="20"/>
+      <c r="G117" s="21"/>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
       <c r="J117" s="1"/>
@@ -4399,19 +4394,17 @@
       <c r="Y117" s="1"/>
     </row>
     <row r="118" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="13">
-        <v>5</v>
+      <c r="A118" s="25" t="s">
+        <v>71</v>
       </c>
-      <c r="B118" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="C118" s="28"/>
-      <c r="D118" s="28"/>
-      <c r="E118" s="28"/>
-      <c r="F118" s="28"/>
-      <c r="G118" s="29"/>
-      <c r="H118" s="4"/>
-      <c r="I118" s="4"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="23"/>
+      <c r="D118" s="23"/>
+      <c r="E118" s="23"/>
+      <c r="F118" s="23"/>
+      <c r="G118" s="23"/>
+      <c r="H118" s="23"/>
+      <c r="I118" s="24"/>
       <c r="J118" s="1"/>
       <c r="K118" s="1"/>
       <c r="L118" s="1"/>
@@ -4430,19 +4423,15 @@
       <c r="Y118" s="1"/>
     </row>
     <row r="119" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="13">
-        <v>6</v>
-      </c>
-      <c r="B119" s="50" t="s">
-        <v>73</v>
-      </c>
-      <c r="C119" s="28"/>
-      <c r="D119" s="28"/>
-      <c r="E119" s="28"/>
-      <c r="F119" s="28"/>
-      <c r="G119" s="29"/>
-      <c r="H119" s="4"/>
-      <c r="I119" s="4"/>
+      <c r="A119" s="27"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="23"/>
+      <c r="D119" s="23"/>
+      <c r="E119" s="23"/>
+      <c r="F119" s="23"/>
+      <c r="G119" s="23"/>
+      <c r="H119" s="23"/>
+      <c r="I119" s="24"/>
       <c r="J119" s="1"/>
       <c r="K119" s="1"/>
       <c r="L119" s="1"/>
@@ -4461,19 +4450,15 @@
       <c r="Y119" s="1"/>
     </row>
     <row r="120" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="13">
-        <v>7</v>
-      </c>
-      <c r="B120" s="50" t="s">
-        <v>74</v>
-      </c>
-      <c r="C120" s="28"/>
-      <c r="D120" s="28"/>
-      <c r="E120" s="28"/>
-      <c r="F120" s="28"/>
-      <c r="G120" s="29"/>
-      <c r="H120" s="4"/>
-      <c r="I120" s="4"/>
+      <c r="A120" s="27"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
+      <c r="D120" s="23"/>
+      <c r="E120" s="23"/>
+      <c r="F120" s="23"/>
+      <c r="G120" s="23"/>
+      <c r="H120" s="23"/>
+      <c r="I120" s="24"/>
       <c r="J120" s="1"/>
       <c r="K120" s="1"/>
       <c r="L120" s="1"/>
@@ -4492,19 +4477,15 @@
       <c r="Y120" s="1"/>
     </row>
     <row r="121" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="13">
-        <v>8</v>
-      </c>
-      <c r="B121" s="50" t="s">
-        <v>75</v>
-      </c>
-      <c r="C121" s="28"/>
-      <c r="D121" s="28"/>
-      <c r="E121" s="28"/>
-      <c r="F121" s="28"/>
-      <c r="G121" s="29"/>
-      <c r="H121" s="4"/>
-      <c r="I121" s="4"/>
+      <c r="A121" s="27"/>
+      <c r="B121" s="23"/>
+      <c r="C121" s="23"/>
+      <c r="D121" s="23"/>
+      <c r="E121" s="23"/>
+      <c r="F121" s="23"/>
+      <c r="G121" s="23"/>
+      <c r="H121" s="23"/>
+      <c r="I121" s="24"/>
       <c r="J121" s="1"/>
       <c r="K121" s="1"/>
       <c r="L121" s="1"/>
@@ -4523,19 +4504,15 @@
       <c r="Y121" s="1"/>
     </row>
     <row r="122" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="13">
-        <v>9</v>
-      </c>
-      <c r="B122" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="C122" s="28"/>
-      <c r="D122" s="28"/>
-      <c r="E122" s="28"/>
-      <c r="F122" s="28"/>
-      <c r="G122" s="29"/>
-      <c r="H122" s="4"/>
-      <c r="I122" s="4"/>
+      <c r="A122" s="27"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
+      <c r="D122" s="23"/>
+      <c r="E122" s="23"/>
+      <c r="F122" s="23"/>
+      <c r="G122" s="23"/>
+      <c r="H122" s="23"/>
+      <c r="I122" s="24"/>
       <c r="J122" s="1"/>
       <c r="K122" s="1"/>
       <c r="L122" s="1"/>
@@ -4554,19 +4531,15 @@
       <c r="Y122" s="1"/>
     </row>
     <row r="123" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="13">
-        <v>10</v>
-      </c>
-      <c r="B123" s="50" t="s">
-        <v>77</v>
-      </c>
-      <c r="C123" s="28"/>
-      <c r="D123" s="28"/>
-      <c r="E123" s="28"/>
-      <c r="F123" s="28"/>
-      <c r="G123" s="29"/>
-      <c r="H123" s="4"/>
-      <c r="I123" s="4"/>
+      <c r="A123" s="27"/>
+      <c r="B123" s="23"/>
+      <c r="C123" s="23"/>
+      <c r="D123" s="23"/>
+      <c r="E123" s="23"/>
+      <c r="F123" s="23"/>
+      <c r="G123" s="23"/>
+      <c r="H123" s="23"/>
+      <c r="I123" s="24"/>
       <c r="J123" s="1"/>
       <c r="K123" s="1"/>
       <c r="L123" s="1"/>
@@ -4585,19 +4558,17 @@
       <c r="Y123" s="1"/>
     </row>
     <row r="124" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="13">
-        <v>11</v>
+      <c r="A124" s="25" t="s">
+        <v>72</v>
       </c>
-      <c r="B124" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C124" s="28"/>
-      <c r="D124" s="28"/>
-      <c r="E124" s="28"/>
-      <c r="F124" s="28"/>
-      <c r="G124" s="29"/>
-      <c r="H124" s="4"/>
-      <c r="I124" s="4"/>
+      <c r="B124" s="23"/>
+      <c r="C124" s="23"/>
+      <c r="D124" s="23"/>
+      <c r="E124" s="23"/>
+      <c r="F124" s="23"/>
+      <c r="G124" s="23"/>
+      <c r="H124" s="23"/>
+      <c r="I124" s="24"/>
       <c r="J124" s="1"/>
       <c r="K124" s="1"/>
       <c r="L124" s="1"/>
@@ -4616,19 +4587,15 @@
       <c r="Y124" s="1"/>
     </row>
     <row r="125" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="13">
-        <v>12</v>
-      </c>
-      <c r="B125" s="50" t="s">
-        <v>79</v>
-      </c>
-      <c r="C125" s="28"/>
-      <c r="D125" s="28"/>
-      <c r="E125" s="28"/>
-      <c r="F125" s="28"/>
-      <c r="G125" s="29"/>
-      <c r="H125" s="4"/>
-      <c r="I125" s="4"/>
+      <c r="A125" s="22"/>
+      <c r="B125" s="23"/>
+      <c r="C125" s="23"/>
+      <c r="D125" s="23"/>
+      <c r="E125" s="23"/>
+      <c r="F125" s="23"/>
+      <c r="G125" s="23"/>
+      <c r="H125" s="23"/>
+      <c r="I125" s="24"/>
       <c r="J125" s="1"/>
       <c r="K125" s="1"/>
       <c r="L125" s="1"/>
@@ -4647,17 +4614,15 @@
       <c r="Y125" s="1"/>
     </row>
     <row r="126" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="B126" s="15"/>
-      <c r="C126" s="15"/>
-      <c r="D126" s="15"/>
-      <c r="E126" s="15"/>
-      <c r="F126" s="15"/>
-      <c r="G126" s="15"/>
-      <c r="H126" s="15"/>
-      <c r="I126" s="16"/>
+      <c r="A126" s="22"/>
+      <c r="B126" s="23"/>
+      <c r="C126" s="23"/>
+      <c r="D126" s="23"/>
+      <c r="E126" s="23"/>
+      <c r="F126" s="23"/>
+      <c r="G126" s="23"/>
+      <c r="H126" s="23"/>
+      <c r="I126" s="24"/>
       <c r="J126" s="1"/>
       <c r="K126" s="1"/>
       <c r="L126" s="1"/>
@@ -4676,15 +4641,15 @@
       <c r="Y126" s="1"/>
     </row>
     <row r="127" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="51"/>
-      <c r="B127" s="15"/>
-      <c r="C127" s="15"/>
-      <c r="D127" s="15"/>
-      <c r="E127" s="15"/>
-      <c r="F127" s="15"/>
-      <c r="G127" s="15"/>
-      <c r="H127" s="15"/>
-      <c r="I127" s="16"/>
+      <c r="A127" s="22"/>
+      <c r="B127" s="23"/>
+      <c r="C127" s="23"/>
+      <c r="D127" s="23"/>
+      <c r="E127" s="23"/>
+      <c r="F127" s="23"/>
+      <c r="G127" s="23"/>
+      <c r="H127" s="23"/>
+      <c r="I127" s="24"/>
       <c r="J127" s="1"/>
       <c r="K127" s="1"/>
       <c r="L127" s="1"/>
@@ -4703,17 +4668,15 @@
       <c r="Y127" s="1"/>
     </row>
     <row r="128" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="B128" s="15"/>
-      <c r="C128" s="15"/>
-      <c r="D128" s="15"/>
-      <c r="E128" s="15"/>
-      <c r="F128" s="15"/>
-      <c r="G128" s="15"/>
-      <c r="H128" s="15"/>
-      <c r="I128" s="16"/>
+      <c r="A128" s="22"/>
+      <c r="B128" s="23"/>
+      <c r="C128" s="23"/>
+      <c r="D128" s="23"/>
+      <c r="E128" s="23"/>
+      <c r="F128" s="23"/>
+      <c r="G128" s="23"/>
+      <c r="H128" s="23"/>
+      <c r="I128" s="24"/>
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
@@ -4732,15 +4695,15 @@
       <c r="Y128" s="1"/>
     </row>
     <row r="129" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="52"/>
-      <c r="B129" s="15"/>
-      <c r="C129" s="15"/>
-      <c r="D129" s="15"/>
-      <c r="E129" s="15"/>
-      <c r="F129" s="15"/>
-      <c r="G129" s="15"/>
-      <c r="H129" s="15"/>
-      <c r="I129" s="16"/>
+      <c r="A129" s="22"/>
+      <c r="B129" s="23"/>
+      <c r="C129" s="23"/>
+      <c r="D129" s="23"/>
+      <c r="E129" s="23"/>
+      <c r="F129" s="23"/>
+      <c r="G129" s="23"/>
+      <c r="H129" s="23"/>
+      <c r="I129" s="24"/>
       <c r="J129" s="1"/>
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
@@ -4759,15 +4722,17 @@
       <c r="Y129" s="1"/>
     </row>
     <row r="130" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="52"/>
-      <c r="B130" s="15"/>
-      <c r="C130" s="15"/>
-      <c r="D130" s="15"/>
-      <c r="E130" s="15"/>
-      <c r="F130" s="15"/>
-      <c r="G130" s="15"/>
-      <c r="H130" s="15"/>
-      <c r="I130" s="16"/>
+      <c r="A130" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="B130" s="23"/>
+      <c r="C130" s="23"/>
+      <c r="D130" s="23"/>
+      <c r="E130" s="23"/>
+      <c r="F130" s="23"/>
+      <c r="G130" s="23"/>
+      <c r="H130" s="23"/>
+      <c r="I130" s="24"/>
       <c r="J130" s="1"/>
       <c r="K130" s="1"/>
       <c r="L130" s="1"/>
@@ -4786,15 +4751,15 @@
       <c r="Y130" s="1"/>
     </row>
     <row r="131" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="52"/>
-      <c r="B131" s="15"/>
-      <c r="C131" s="15"/>
-      <c r="D131" s="15"/>
-      <c r="E131" s="15"/>
-      <c r="F131" s="15"/>
-      <c r="G131" s="15"/>
-      <c r="H131" s="15"/>
-      <c r="I131" s="16"/>
+      <c r="A131" s="19"/>
+      <c r="B131" s="20"/>
+      <c r="C131" s="20"/>
+      <c r="D131" s="20"/>
+      <c r="E131" s="20"/>
+      <c r="F131" s="20"/>
+      <c r="G131" s="20"/>
+      <c r="H131" s="20"/>
+      <c r="I131" s="21"/>
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
@@ -4813,17 +4778,15 @@
       <c r="Y131" s="1"/>
     </row>
     <row r="132" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="B132" s="15"/>
-      <c r="C132" s="15"/>
-      <c r="D132" s="15"/>
-      <c r="E132" s="15"/>
-      <c r="F132" s="15"/>
-      <c r="G132" s="15"/>
-      <c r="H132" s="15"/>
-      <c r="I132" s="16"/>
+      <c r="A132" s="19"/>
+      <c r="B132" s="20"/>
+      <c r="C132" s="20"/>
+      <c r="D132" s="20"/>
+      <c r="E132" s="20"/>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="20"/>
+      <c r="I132" s="21"/>
       <c r="J132" s="1"/>
       <c r="K132" s="1"/>
       <c r="L132" s="1"/>
@@ -4842,15 +4805,15 @@
       <c r="Y132" s="1"/>
     </row>
     <row r="133" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="53"/>
-      <c r="B133" s="28"/>
-      <c r="C133" s="28"/>
-      <c r="D133" s="28"/>
-      <c r="E133" s="28"/>
-      <c r="F133" s="28"/>
-      <c r="G133" s="28"/>
-      <c r="H133" s="28"/>
-      <c r="I133" s="29"/>
+      <c r="A133" s="19"/>
+      <c r="B133" s="20"/>
+      <c r="C133" s="20"/>
+      <c r="D133" s="20"/>
+      <c r="E133" s="20"/>
+      <c r="F133" s="20"/>
+      <c r="G133" s="20"/>
+      <c r="H133" s="20"/>
+      <c r="I133" s="21"/>
       <c r="J133" s="1"/>
       <c r="K133" s="1"/>
       <c r="L133" s="1"/>
@@ -4869,15 +4832,15 @@
       <c r="Y133" s="1"/>
     </row>
     <row r="134" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="53"/>
-      <c r="B134" s="28"/>
-      <c r="C134" s="28"/>
-      <c r="D134" s="28"/>
-      <c r="E134" s="28"/>
-      <c r="F134" s="28"/>
-      <c r="G134" s="28"/>
-      <c r="H134" s="28"/>
-      <c r="I134" s="29"/>
+      <c r="A134" s="19"/>
+      <c r="B134" s="20"/>
+      <c r="C134" s="20"/>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20"/>
+      <c r="F134" s="20"/>
+      <c r="G134" s="20"/>
+      <c r="H134" s="20"/>
+      <c r="I134" s="21"/>
       <c r="J134" s="1"/>
       <c r="K134" s="1"/>
       <c r="L134" s="1"/>
@@ -4896,15 +4859,15 @@
       <c r="Y134" s="1"/>
     </row>
     <row r="135" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
-      <c r="C135" s="1"/>
-      <c r="D135" s="1"/>
-      <c r="E135" s="1"/>
-      <c r="F135" s="1"/>
-      <c r="G135" s="1"/>
-      <c r="H135" s="1"/>
-      <c r="I135" s="1"/>
+      <c r="A135" s="19"/>
+      <c r="B135" s="20"/>
+      <c r="C135" s="20"/>
+      <c r="D135" s="20"/>
+      <c r="E135" s="20"/>
+      <c r="F135" s="20"/>
+      <c r="G135" s="20"/>
+      <c r="H135" s="20"/>
+      <c r="I135" s="21"/>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
@@ -11078,87 +11041,116 @@
       <c r="X363" s="1"/>
       <c r="Y363" s="1"/>
     </row>
+    <row r="364" spans="1:25" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A364" s="1"/>
+      <c r="B364" s="1"/>
+      <c r="C364" s="1"/>
+      <c r="D364" s="1"/>
+      <c r="E364" s="1"/>
+      <c r="F364" s="1"/>
+      <c r="G364" s="1"/>
+      <c r="H364" s="1"/>
+      <c r="I364" s="1"/>
+      <c r="J364" s="1"/>
+      <c r="K364" s="1"/>
+      <c r="L364" s="1"/>
+      <c r="M364" s="1"/>
+      <c r="N364" s="1"/>
+      <c r="O364" s="1"/>
+      <c r="P364" s="1"/>
+      <c r="Q364" s="1"/>
+      <c r="R364" s="1"/>
+      <c r="S364" s="1"/>
+      <c r="T364" s="1"/>
+      <c r="U364" s="1"/>
+      <c r="V364" s="1"/>
+      <c r="W364" s="1"/>
+      <c r="X364" s="1"/>
+      <c r="Y364" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="75">
-    <mergeCell ref="A134:I134"/>
-    <mergeCell ref="A129:I129"/>
-    <mergeCell ref="A130:I130"/>
-    <mergeCell ref="A131:I131"/>
-    <mergeCell ref="A132:I132"/>
-    <mergeCell ref="A133:I133"/>
-    <mergeCell ref="B124:G124"/>
-    <mergeCell ref="B125:G125"/>
-    <mergeCell ref="A126:I126"/>
-    <mergeCell ref="A127:I127"/>
-    <mergeCell ref="A128:I128"/>
-    <mergeCell ref="B119:G119"/>
-    <mergeCell ref="B120:G120"/>
-    <mergeCell ref="B121:G121"/>
-    <mergeCell ref="B122:G122"/>
-    <mergeCell ref="B123:G123"/>
+  <mergeCells count="78">
+    <mergeCell ref="A1:I2"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A5:I5"/>
+    <mergeCell ref="C8:I9"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="F10:I10"/>
+    <mergeCell ref="E11:E25"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D25"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="H24:I25"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="A68:C68"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="G68:I68"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="G47:I47"/>
+    <mergeCell ref="A89:C89"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="G89:I89"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="F91:I91"/>
+    <mergeCell ref="D91:D99"/>
+    <mergeCell ref="G92:I92"/>
+    <mergeCell ref="G93:I93"/>
+    <mergeCell ref="G94:I94"/>
+    <mergeCell ref="G95:I95"/>
+    <mergeCell ref="G96:I96"/>
+    <mergeCell ref="G97:I97"/>
+    <mergeCell ref="G98:I98"/>
+    <mergeCell ref="G99:I99"/>
+    <mergeCell ref="G100:I100"/>
+    <mergeCell ref="G101:I101"/>
+    <mergeCell ref="G102:I102"/>
+    <mergeCell ref="A104:I104"/>
+    <mergeCell ref="B105:G105"/>
+    <mergeCell ref="B106:G106"/>
+    <mergeCell ref="B107:G107"/>
+    <mergeCell ref="B108:G108"/>
+    <mergeCell ref="B109:G109"/>
+    <mergeCell ref="B110:G110"/>
+    <mergeCell ref="B111:G111"/>
+    <mergeCell ref="B112:G112"/>
+    <mergeCell ref="B113:G113"/>
     <mergeCell ref="B114:G114"/>
     <mergeCell ref="B115:G115"/>
     <mergeCell ref="B116:G116"/>
     <mergeCell ref="B117:G117"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="G108:I108"/>
-    <mergeCell ref="G109:I109"/>
-    <mergeCell ref="G110:I110"/>
-    <mergeCell ref="A112:I112"/>
-    <mergeCell ref="B113:G113"/>
-    <mergeCell ref="A97:C97"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="G97:I97"/>
-    <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="F99:I99"/>
-    <mergeCell ref="D99:D107"/>
-    <mergeCell ref="G100:I100"/>
-    <mergeCell ref="G101:I101"/>
-    <mergeCell ref="G102:I102"/>
-    <mergeCell ref="G103:I103"/>
-    <mergeCell ref="G104:I104"/>
-    <mergeCell ref="G105:I105"/>
-    <mergeCell ref="G106:I106"/>
-    <mergeCell ref="G107:I107"/>
-    <mergeCell ref="A76:C76"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="G76:I76"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="A55:C55"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="G55:I55"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="F18:I18"/>
-    <mergeCell ref="E19:E33"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:D33"/>
-    <mergeCell ref="F32:G32"/>
-    <mergeCell ref="H32:I33"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="F33:G33"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A13:B17"/>
-    <mergeCell ref="C13:I13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="E16:I17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:B11"/>
-    <mergeCell ref="D3:I3"/>
-    <mergeCell ref="D4:I4"/>
-    <mergeCell ref="D5:I5"/>
-    <mergeCell ref="D6:I6"/>
-    <mergeCell ref="D7:I7"/>
-    <mergeCell ref="D8:I8"/>
-    <mergeCell ref="D9:I9"/>
-    <mergeCell ref="D10:I10"/>
-    <mergeCell ref="D11:I11"/>
+    <mergeCell ref="A118:I118"/>
+    <mergeCell ref="A123:I123"/>
+    <mergeCell ref="A124:I124"/>
+    <mergeCell ref="A122:I122"/>
+    <mergeCell ref="A121:I121"/>
+    <mergeCell ref="A120:I120"/>
+    <mergeCell ref="A119:I119"/>
+    <mergeCell ref="A135:I135"/>
+    <mergeCell ref="A125:I125"/>
+    <mergeCell ref="A128:I128"/>
+    <mergeCell ref="A129:I129"/>
+    <mergeCell ref="A130:I130"/>
+    <mergeCell ref="A131:I131"/>
+    <mergeCell ref="A127:I127"/>
+    <mergeCell ref="A126:I126"/>
+    <mergeCell ref="A134:I134"/>
+    <mergeCell ref="A133:I133"/>
+    <mergeCell ref="A132:I132"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="14" pageOrder="overThenDown" orientation="portrait" cellComments="atEnd"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>